--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -4610,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329061</v>
+        <v>118329123</v>
       </c>
       <c r="B37" t="n">
-        <v>82263</v>
+        <v>96801</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539169</v>
+        <v>539449</v>
       </c>
       <c r="R37" t="n">
-        <v>7198790</v>
+        <v>7199143</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4722,10 +4722,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329077</v>
+        <v>118329061</v>
       </c>
       <c r="B38" t="n">
-        <v>86820</v>
+        <v>82263</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,21 +4738,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539355</v>
+        <v>539169</v>
       </c>
       <c r="R38" t="n">
-        <v>7198883</v>
+        <v>7198790</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329085</v>
+        <v>118329077</v>
       </c>
       <c r="B39" t="n">
-        <v>79600</v>
+        <v>86820</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,25 +4846,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539640</v>
+        <v>539355</v>
       </c>
       <c r="R39" t="n">
-        <v>7198849</v>
+        <v>7198883</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329112</v>
+        <v>118329085</v>
       </c>
       <c r="B40" t="n">
-        <v>91196</v>
+        <v>79600</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539541</v>
+        <v>539640</v>
       </c>
       <c r="R40" t="n">
-        <v>7199130</v>
+        <v>7198849</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,10 +5058,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329123</v>
+        <v>118329112</v>
       </c>
       <c r="B41" t="n">
-        <v>96801</v>
+        <v>91196</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,21 +5074,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539449</v>
+        <v>539541</v>
       </c>
       <c r="R41" t="n">
-        <v>7199143</v>
+        <v>7199130</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6526,10 +6526,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118329052</v>
+        <v>118329095</v>
       </c>
       <c r="B54" t="n">
-        <v>79601</v>
+        <v>57306</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6538,38 +6538,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539175</v>
+        <v>539705</v>
       </c>
       <c r="R54" t="n">
-        <v>7199100</v>
+        <v>7198856</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6601,7 +6606,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6611,7 +6616,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6638,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118329073</v>
+        <v>118329052</v>
       </c>
       <c r="B55" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6650,25 +6655,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6678,10 +6683,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539301</v>
+        <v>539175</v>
       </c>
       <c r="R55" t="n">
-        <v>7198925</v>
+        <v>7199100</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6713,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6723,7 +6728,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6750,10 +6755,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118329095</v>
+        <v>118329073</v>
       </c>
       <c r="B56" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6766,39 +6771,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539705</v>
+        <v>539301</v>
       </c>
       <c r="R56" t="n">
-        <v>7198856</v>
+        <v>7198925</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7427,10 +7427,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329069</v>
+        <v>118329059</v>
       </c>
       <c r="B62" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7443,21 +7443,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539197</v>
+        <v>539179</v>
       </c>
       <c r="R62" t="n">
-        <v>7198784</v>
+        <v>7198796</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7539,7 +7539,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329131</v>
+        <v>118329069</v>
       </c>
       <c r="B63" t="n">
         <v>78484</v>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539434</v>
+        <v>539197</v>
       </c>
       <c r="R63" t="n">
-        <v>7199188</v>
+        <v>7198784</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7651,10 +7651,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118329059</v>
+        <v>118329131</v>
       </c>
       <c r="B64" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7667,21 +7667,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539179</v>
+        <v>539434</v>
       </c>
       <c r="R64" t="n">
-        <v>7198796</v>
+        <v>7199188</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7875,10 +7875,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118329098</v>
+        <v>118329113</v>
       </c>
       <c r="B66" t="n">
-        <v>79566</v>
+        <v>78484</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539698</v>
+        <v>539540</v>
       </c>
       <c r="R66" t="n">
-        <v>7198870</v>
+        <v>7199128</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7987,10 +7987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118329113</v>
+        <v>118329090</v>
       </c>
       <c r="B67" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539540</v>
+        <v>539689</v>
       </c>
       <c r="R67" t="n">
-        <v>7199128</v>
+        <v>7198811</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,10 +8099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118329090</v>
+        <v>118329098</v>
       </c>
       <c r="B68" t="n">
-        <v>79565</v>
+        <v>79566</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539689</v>
+        <v>539698</v>
       </c>
       <c r="R68" t="n">
-        <v>7198811</v>
+        <v>7198870</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9224,10 +9224,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118329133</v>
+        <v>118329109</v>
       </c>
       <c r="B78" t="n">
-        <v>97867</v>
+        <v>90500</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9236,25 +9236,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539424</v>
+        <v>539520</v>
       </c>
       <c r="R78" t="n">
-        <v>7199232</v>
+        <v>7199044</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9336,10 +9336,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118329109</v>
+        <v>118329118</v>
       </c>
       <c r="B79" t="n">
-        <v>90500</v>
+        <v>90896</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9352,21 +9352,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9376,10 +9371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539520</v>
+        <v>539499</v>
       </c>
       <c r="R79" t="n">
-        <v>7199044</v>
+        <v>7199150</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9411,7 +9406,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9421,7 +9416,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9560,10 +9555,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118329118</v>
+        <v>118329133</v>
       </c>
       <c r="B81" t="n">
-        <v>90896</v>
+        <v>97867</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9572,20 +9567,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6040186</v>
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539499</v>
+        <v>539424</v>
       </c>
       <c r="R81" t="n">
-        <v>7199150</v>
+        <v>7199232</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -4610,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329123</v>
+        <v>118329061</v>
       </c>
       <c r="B37" t="n">
-        <v>96801</v>
+        <v>82263</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539449</v>
+        <v>539169</v>
       </c>
       <c r="R37" t="n">
-        <v>7199143</v>
+        <v>7198790</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4722,10 +4722,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329061</v>
+        <v>118329077</v>
       </c>
       <c r="B38" t="n">
-        <v>82263</v>
+        <v>86820</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,21 +4738,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539169</v>
+        <v>539355</v>
       </c>
       <c r="R38" t="n">
-        <v>7198790</v>
+        <v>7198883</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329077</v>
+        <v>118329085</v>
       </c>
       <c r="B39" t="n">
-        <v>86820</v>
+        <v>79600</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,25 +4846,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539355</v>
+        <v>539640</v>
       </c>
       <c r="R39" t="n">
-        <v>7198883</v>
+        <v>7198849</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329085</v>
+        <v>118329112</v>
       </c>
       <c r="B40" t="n">
-        <v>79600</v>
+        <v>91196</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539640</v>
+        <v>539541</v>
       </c>
       <c r="R40" t="n">
-        <v>7198849</v>
+        <v>7199130</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,10 +5058,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329112</v>
+        <v>118329123</v>
       </c>
       <c r="B41" t="n">
-        <v>91196</v>
+        <v>96801</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,21 +5074,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539541</v>
+        <v>539449</v>
       </c>
       <c r="R41" t="n">
-        <v>7199130</v>
+        <v>7199143</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,10 +5170,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118329080</v>
+        <v>118329137</v>
       </c>
       <c r="B42" t="n">
-        <v>90451</v>
+        <v>74596</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5186,21 +5186,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539383</v>
+        <v>539448</v>
       </c>
       <c r="R42" t="n">
-        <v>7198860</v>
+        <v>7199233</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,10 +5282,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329137</v>
+        <v>118329071</v>
       </c>
       <c r="B43" t="n">
-        <v>74596</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539448</v>
+        <v>539291</v>
       </c>
       <c r="R43" t="n">
-        <v>7199233</v>
+        <v>7198926</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329071</v>
+        <v>118329080</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>90451</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539291</v>
+        <v>539383</v>
       </c>
       <c r="R44" t="n">
-        <v>7198926</v>
+        <v>7198860</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329068</v>
+        <v>118329110</v>
       </c>
       <c r="B3" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539196</v>
+        <v>539520</v>
       </c>
       <c r="R3" t="n">
-        <v>7198782</v>
+        <v>7199050</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329091</v>
+        <v>118329109</v>
       </c>
       <c r="B4" t="n">
-        <v>79566</v>
+        <v>90500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539689</v>
+        <v>539520</v>
       </c>
       <c r="R4" t="n">
-        <v>7198809</v>
+        <v>7199044</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329116</v>
+        <v>118329054</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539546</v>
+        <v>539175</v>
       </c>
       <c r="R5" t="n">
-        <v>7199128</v>
+        <v>7199103</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118329056</v>
+        <v>118329118</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>90896</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1140,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539183</v>
+        <v>539499</v>
       </c>
       <c r="R6" t="n">
-        <v>7198843</v>
+        <v>7199150</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1204,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329143</v>
+        <v>118329114</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>79566</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539470</v>
+        <v>539540</v>
       </c>
       <c r="R7" t="n">
-        <v>7199251</v>
+        <v>7199126</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329110</v>
+        <v>118329137</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>74596</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539520</v>
+        <v>539448</v>
       </c>
       <c r="R8" t="n">
-        <v>7199050</v>
+        <v>7199233</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329094</v>
+        <v>118329100</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539687</v>
+        <v>539698</v>
       </c>
       <c r="R9" t="n">
-        <v>7198809</v>
+        <v>7198866</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329083</v>
+        <v>118329056</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,48 +1583,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539604</v>
+        <v>539183</v>
       </c>
       <c r="R10" t="n">
-        <v>7198880</v>
+        <v>7198843</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329070</v>
+        <v>118329104</v>
       </c>
       <c r="B11" t="n">
-        <v>90896</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,16 +1695,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539292</v>
+        <v>539613</v>
       </c>
       <c r="R11" t="n">
-        <v>7198929</v>
+        <v>7198921</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329125</v>
+        <v>118329053</v>
       </c>
       <c r="B12" t="n">
-        <v>90788</v>
+        <v>79594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,25 +1803,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539448</v>
+        <v>539176</v>
       </c>
       <c r="R12" t="n">
-        <v>7199144</v>
+        <v>7199101</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329084</v>
+        <v>118329106</v>
       </c>
       <c r="B13" t="n">
-        <v>79601</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,38 +1915,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539643</v>
+        <v>539537</v>
       </c>
       <c r="R13" t="n">
-        <v>7198846</v>
+        <v>7199040</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118329062</v>
+        <v>118329069</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -2069,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539168</v>
+        <v>539197</v>
       </c>
       <c r="R14" t="n">
-        <v>7198788</v>
+        <v>7198784</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118329076</v>
+        <v>118329126</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2181,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539323</v>
+        <v>539448</v>
       </c>
       <c r="R15" t="n">
-        <v>7198881</v>
+        <v>7199142</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118329114</v>
+        <v>118329079</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539540</v>
+        <v>539381</v>
       </c>
       <c r="R16" t="n">
-        <v>7199126</v>
+        <v>7198861</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329127</v>
+        <v>118329074</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2372,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539435</v>
+        <v>539323</v>
       </c>
       <c r="R17" t="n">
-        <v>7199161</v>
+        <v>7198881</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,7 +2468,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118329126</v>
+        <v>118329094</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2517,10 +2508,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539448</v>
+        <v>539687</v>
       </c>
       <c r="R18" t="n">
-        <v>7199142</v>
+        <v>7198809</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329107</v>
+        <v>118329103</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>56502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,38 +2592,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539536</v>
+        <v>539613</v>
       </c>
       <c r="R19" t="n">
-        <v>7199040</v>
+        <v>7198921</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329105</v>
+        <v>118329097</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2714,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539569</v>
+        <v>539700</v>
       </c>
       <c r="R20" t="n">
-        <v>7199018</v>
+        <v>7198865</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329099</v>
+        <v>118329062</v>
       </c>
       <c r="B21" t="n">
-        <v>104925</v>
+        <v>78484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,25 +2826,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539699</v>
+        <v>539168</v>
       </c>
       <c r="R21" t="n">
-        <v>7198868</v>
+        <v>7198788</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329111</v>
+        <v>118329076</v>
       </c>
       <c r="B22" t="n">
-        <v>82263</v>
+        <v>78484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2942,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539540</v>
+        <v>539323</v>
       </c>
       <c r="R22" t="n">
-        <v>7199131</v>
+        <v>7198881</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329121</v>
+        <v>118329072</v>
       </c>
       <c r="B23" t="n">
-        <v>90522</v>
+        <v>57306</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,34 +3054,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539470</v>
+        <v>539301</v>
       </c>
       <c r="R23" t="n">
-        <v>7199132</v>
+        <v>7198925</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329136</v>
+        <v>118329052</v>
       </c>
       <c r="B24" t="n">
-        <v>77421</v>
+        <v>79601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,25 +3167,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3195,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539445</v>
+        <v>539175</v>
       </c>
       <c r="R24" t="n">
-        <v>7199236</v>
+        <v>7199100</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3230,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3240,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3267,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329087</v>
+        <v>118329127</v>
       </c>
       <c r="B25" t="n">
-        <v>79594</v>
+        <v>90504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,25 +3279,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539639</v>
+        <v>539435</v>
       </c>
       <c r="R25" t="n">
-        <v>7198854</v>
+        <v>7199161</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3342,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3352,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118329065</v>
+        <v>118329078</v>
       </c>
       <c r="B26" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,21 +3395,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539189</v>
+        <v>539351</v>
       </c>
       <c r="R26" t="n">
-        <v>7198737</v>
+        <v>7198894</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3454,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3464,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329119</v>
+        <v>118329124</v>
       </c>
       <c r="B27" t="n">
-        <v>82263</v>
+        <v>90858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,25 +3503,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3531,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539499</v>
+        <v>539448</v>
       </c>
       <c r="R27" t="n">
-        <v>7199152</v>
+        <v>7199143</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3560,7 +3566,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3576,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,10 +3603,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329124</v>
+        <v>118329060</v>
       </c>
       <c r="B28" t="n">
-        <v>90858</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,25 +3615,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3643,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539448</v>
+        <v>539179</v>
       </c>
       <c r="R28" t="n">
-        <v>7199143</v>
+        <v>7198796</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3672,7 +3678,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,7 +3688,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,7 +3715,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329054</v>
+        <v>118329071</v>
       </c>
       <c r="B29" t="n">
         <v>78484</v>
@@ -3749,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539175</v>
+        <v>539291</v>
       </c>
       <c r="R29" t="n">
-        <v>7199103</v>
+        <v>7198926</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3784,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329104</v>
+        <v>118329050</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>94250</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,25 +3839,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3861,10 +3867,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539613</v>
+        <v>539191</v>
       </c>
       <c r="R30" t="n">
-        <v>7198921</v>
+        <v>7199130</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3896,7 +3902,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3912,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,7 +3939,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329122</v>
+        <v>118329067</v>
       </c>
       <c r="B31" t="n">
         <v>78484</v>
@@ -3973,10 +3979,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539468</v>
+        <v>539188</v>
       </c>
       <c r="R31" t="n">
-        <v>7199130</v>
+        <v>7198737</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4008,7 +4014,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4024,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,10 +4051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329067</v>
+        <v>118329081</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,34 +4067,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539188</v>
+        <v>539471</v>
       </c>
       <c r="R32" t="n">
-        <v>7198737</v>
+        <v>7198904</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4120,7 +4131,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4141,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,10 +4168,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329092</v>
+        <v>118329055</v>
       </c>
       <c r="B33" t="n">
-        <v>79601</v>
+        <v>90500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,25 +4180,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4197,10 +4208,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539689</v>
+        <v>539176</v>
       </c>
       <c r="R33" t="n">
-        <v>7198809</v>
+        <v>7198838</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4232,7 +4243,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4242,7 +4253,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329064</v>
+        <v>118329092</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4281,25 +4292,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4309,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539166</v>
+        <v>539689</v>
       </c>
       <c r="R34" t="n">
-        <v>7198776</v>
+        <v>7198809</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4344,7 +4355,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4354,7 +4365,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329055</v>
+        <v>118329112</v>
       </c>
       <c r="B35" t="n">
-        <v>90500</v>
+        <v>91196</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4393,25 +4404,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4421,10 +4432,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539176</v>
+        <v>539541</v>
       </c>
       <c r="R35" t="n">
-        <v>7198838</v>
+        <v>7199130</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4456,7 +4467,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4466,7 +4477,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118329072</v>
+        <v>118329107</v>
       </c>
       <c r="B36" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,39 +4520,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539301</v>
+        <v>539536</v>
       </c>
       <c r="R36" t="n">
-        <v>7198925</v>
+        <v>7199040</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4573,7 +4579,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4583,7 +4589,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4616,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329061</v>
+        <v>118329134</v>
       </c>
       <c r="B37" t="n">
-        <v>82263</v>
+        <v>97766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,27 +4628,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>223597</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4650,10 +4652,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539169</v>
+        <v>539421</v>
       </c>
       <c r="R37" t="n">
-        <v>7198790</v>
+        <v>7199232</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4685,7 +4687,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4695,7 +4697,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4704,6 +4706,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4722,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329077</v>
+        <v>118329116</v>
       </c>
       <c r="B38" t="n">
-        <v>86820</v>
+        <v>78484</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,21 +4741,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4762,10 +4765,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539355</v>
+        <v>539546</v>
       </c>
       <c r="R38" t="n">
-        <v>7198883</v>
+        <v>7199128</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4797,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4807,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,10 +4837,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329085</v>
+        <v>118329064</v>
       </c>
       <c r="B39" t="n">
-        <v>79600</v>
+        <v>78484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,20 +4849,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4874,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539640</v>
+        <v>539166</v>
       </c>
       <c r="R39" t="n">
-        <v>7198849</v>
+        <v>7198776</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4909,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4919,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,10 +4949,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329112</v>
+        <v>118329080</v>
       </c>
       <c r="B40" t="n">
-        <v>91196</v>
+        <v>90451</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4958,25 +4961,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>112</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539541</v>
+        <v>539383</v>
       </c>
       <c r="R40" t="n">
-        <v>7199130</v>
+        <v>7198860</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5021,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5031,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,10 +5061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329123</v>
+        <v>118329063</v>
       </c>
       <c r="B41" t="n">
-        <v>96801</v>
+        <v>96807</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,16 +5077,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5098,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539449</v>
+        <v>539165</v>
       </c>
       <c r="R41" t="n">
-        <v>7199143</v>
+        <v>7198776</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5133,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118329137</v>
+        <v>118329121</v>
       </c>
       <c r="B42" t="n">
-        <v>74596</v>
+        <v>90522</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5186,21 +5189,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5210,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539448</v>
+        <v>539470</v>
       </c>
       <c r="R42" t="n">
-        <v>7199233</v>
+        <v>7199132</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5245,7 +5248,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5255,7 +5258,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,7 +5285,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329071</v>
+        <v>118329139</v>
       </c>
       <c r="B43" t="n">
         <v>78484</v>
@@ -5322,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539291</v>
+        <v>539448</v>
       </c>
       <c r="R43" t="n">
-        <v>7198926</v>
+        <v>7199233</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5357,7 +5360,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5367,7 +5370,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5394,10 +5397,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329080</v>
+        <v>118329128</v>
       </c>
       <c r="B44" t="n">
-        <v>90451</v>
+        <v>78484</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5410,21 +5413,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5434,10 +5437,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539383</v>
+        <v>539438</v>
       </c>
       <c r="R44" t="n">
-        <v>7198860</v>
+        <v>7199164</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5469,7 +5472,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5479,7 +5482,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5506,10 +5509,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329103</v>
+        <v>118329093</v>
       </c>
       <c r="B45" t="n">
-        <v>56502</v>
+        <v>79594</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5522,44 +5525,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539613</v>
+        <v>539687</v>
       </c>
       <c r="R45" t="n">
-        <v>7198921</v>
+        <v>7198809</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5591,7 +5584,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5601,7 +5594,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5628,10 +5621,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329063</v>
+        <v>118329113</v>
       </c>
       <c r="B46" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5640,25 +5633,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5668,10 +5661,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539165</v>
+        <v>539540</v>
       </c>
       <c r="R46" t="n">
-        <v>7198776</v>
+        <v>7199128</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5703,7 +5696,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5713,7 +5706,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5740,10 +5733,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329134</v>
+        <v>118329131</v>
       </c>
       <c r="B47" t="n">
-        <v>97766</v>
+        <v>78484</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5752,23 +5745,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5776,10 +5773,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539421</v>
+        <v>539434</v>
       </c>
       <c r="R47" t="n">
-        <v>7199232</v>
+        <v>7199188</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5811,7 +5808,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5821,7 +5818,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5830,7 +5827,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5849,10 +5845,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329082</v>
+        <v>118329133</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5861,25 +5857,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5889,10 +5885,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539469</v>
+        <v>539424</v>
       </c>
       <c r="R48" t="n">
-        <v>7198907</v>
+        <v>7199232</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5924,7 +5920,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5930,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5961,10 +5957,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118329117</v>
+        <v>118329099</v>
       </c>
       <c r="B49" t="n">
-        <v>78484</v>
+        <v>104925</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5973,25 +5969,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6001,10 +5997,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539502</v>
+        <v>539699</v>
       </c>
       <c r="R49" t="n">
-        <v>7199148</v>
+        <v>7198868</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6036,7 +6032,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6046,7 +6042,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,10 +6069,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118329115</v>
+        <v>118329059</v>
       </c>
       <c r="B50" t="n">
-        <v>79594</v>
+        <v>90522</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,25 +6081,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6113,10 +6109,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539543</v>
+        <v>539179</v>
       </c>
       <c r="R50" t="n">
-        <v>7199127</v>
+        <v>7198796</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6148,7 +6144,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6158,7 +6154,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6185,10 +6181,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118329100</v>
+        <v>118329143</v>
       </c>
       <c r="B51" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6197,25 +6193,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6225,10 +6221,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539698</v>
+        <v>539470</v>
       </c>
       <c r="R51" t="n">
-        <v>7198866</v>
+        <v>7199251</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6260,7 +6256,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6270,7 +6266,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6297,10 +6293,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118329093</v>
+        <v>118329111</v>
       </c>
       <c r="B52" t="n">
-        <v>79594</v>
+        <v>82263</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6309,25 +6305,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6337,10 +6333,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539687</v>
+        <v>539540</v>
       </c>
       <c r="R52" t="n">
-        <v>7198809</v>
+        <v>7199131</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6372,7 +6368,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6382,7 +6378,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6409,10 +6405,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118329106</v>
+        <v>118329122</v>
       </c>
       <c r="B53" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6425,39 +6421,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539537</v>
+        <v>539468</v>
       </c>
       <c r="R53" t="n">
-        <v>7199040</v>
+        <v>7199130</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6489,7 +6480,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6499,7 +6490,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6526,10 +6517,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118329095</v>
+        <v>118329085</v>
       </c>
       <c r="B54" t="n">
-        <v>57306</v>
+        <v>79600</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6538,43 +6529,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539705</v>
+        <v>539640</v>
       </c>
       <c r="R54" t="n">
-        <v>7198856</v>
+        <v>7198849</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6606,7 +6592,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6616,7 +6602,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6643,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118329052</v>
+        <v>118329120</v>
       </c>
       <c r="B55" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6655,25 +6641,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6683,10 +6669,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539175</v>
+        <v>539497</v>
       </c>
       <c r="R55" t="n">
-        <v>7199100</v>
+        <v>7199152</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6718,7 +6704,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,7 +6714,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6755,7 +6741,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118329073</v>
+        <v>118329102</v>
       </c>
       <c r="B56" t="n">
         <v>78484</v>
@@ -6795,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539301</v>
+        <v>539699</v>
       </c>
       <c r="R56" t="n">
-        <v>7198925</v>
+        <v>7198863</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6830,7 +6816,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6840,7 +6826,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6867,10 +6853,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118329097</v>
+        <v>118329083</v>
       </c>
       <c r="B57" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6879,38 +6865,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539700</v>
+        <v>539604</v>
       </c>
       <c r="R57" t="n">
-        <v>7198865</v>
+        <v>7198880</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6979,10 +6979,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118329102</v>
+        <v>118329125</v>
       </c>
       <c r="B58" t="n">
-        <v>78484</v>
+        <v>90788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6995,21 +6995,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539699</v>
+        <v>539448</v>
       </c>
       <c r="R58" t="n">
-        <v>7198863</v>
+        <v>7199144</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7091,10 +7091,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118329058</v>
+        <v>118329077</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>86820</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7107,21 +7107,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539167</v>
+        <v>539355</v>
       </c>
       <c r="R59" t="n">
-        <v>7198820</v>
+        <v>7198883</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7203,10 +7203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118329051</v>
+        <v>118329061</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
+        <v>82263</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7219,21 +7219,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539190</v>
+        <v>539169</v>
       </c>
       <c r="R60" t="n">
-        <v>7199129</v>
+        <v>7198790</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7315,10 +7315,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118329050</v>
+        <v>118329084</v>
       </c>
       <c r="B61" t="n">
-        <v>94250</v>
+        <v>79601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7331,21 +7331,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539191</v>
+        <v>539643</v>
       </c>
       <c r="R61" t="n">
-        <v>7199130</v>
+        <v>7198846</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7427,10 +7427,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329059</v>
+        <v>118329115</v>
       </c>
       <c r="B62" t="n">
-        <v>90522</v>
+        <v>79594</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7439,25 +7439,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539179</v>
+        <v>539543</v>
       </c>
       <c r="R62" t="n">
-        <v>7198796</v>
+        <v>7199127</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329069</v>
+        <v>118329123</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7551,25 +7551,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539197</v>
+        <v>539449</v>
       </c>
       <c r="R63" t="n">
-        <v>7198784</v>
+        <v>7199143</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7651,7 +7651,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118329131</v>
+        <v>118329058</v>
       </c>
       <c r="B64" t="n">
         <v>78484</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539434</v>
+        <v>539167</v>
       </c>
       <c r="R64" t="n">
-        <v>7199188</v>
+        <v>7198820</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7763,10 +7763,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118329138</v>
+        <v>118329065</v>
       </c>
       <c r="B65" t="n">
-        <v>96801</v>
+        <v>90522</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7775,25 +7775,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539448</v>
+        <v>539189</v>
       </c>
       <c r="R65" t="n">
-        <v>7199233</v>
+        <v>7198737</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7875,10 +7875,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118329113</v>
+        <v>118329091</v>
       </c>
       <c r="B66" t="n">
-        <v>78484</v>
+        <v>79566</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7891,21 +7891,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539540</v>
+        <v>539689</v>
       </c>
       <c r="R66" t="n">
-        <v>7199128</v>
+        <v>7198809</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7987,10 +7987,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118329090</v>
+        <v>118329117</v>
       </c>
       <c r="B67" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8003,21 +8003,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8027,10 +8027,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539689</v>
+        <v>539502</v>
       </c>
       <c r="R67" t="n">
-        <v>7198811</v>
+        <v>7199148</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,10 +8099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118329098</v>
+        <v>118329119</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>82263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8115,21 +8115,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539698</v>
+        <v>539499</v>
       </c>
       <c r="R68" t="n">
-        <v>7198870</v>
+        <v>7199152</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8211,10 +8211,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118329074</v>
+        <v>118329105</v>
       </c>
       <c r="B69" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8227,21 +8227,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539323</v>
+        <v>539569</v>
       </c>
       <c r="R69" t="n">
-        <v>7198881</v>
+        <v>7199018</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8323,10 +8323,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118329128</v>
+        <v>118329095</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8339,34 +8339,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539438</v>
+        <v>539705</v>
       </c>
       <c r="R70" t="n">
-        <v>7199164</v>
+        <v>7198856</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8398,7 +8403,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8408,7 +8413,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8435,7 +8440,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118329078</v>
+        <v>118329051</v>
       </c>
       <c r="B71" t="n">
         <v>78484</v>
@@ -8475,10 +8480,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539351</v>
+        <v>539190</v>
       </c>
       <c r="R71" t="n">
-        <v>7198894</v>
+        <v>7199129</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8510,7 +8515,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8520,7 +8525,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8547,10 +8552,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118329120</v>
+        <v>118329068</v>
       </c>
       <c r="B72" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8563,21 +8568,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8587,10 +8592,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539497</v>
+        <v>539196</v>
       </c>
       <c r="R72" t="n">
-        <v>7199152</v>
+        <v>7198782</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8622,7 +8627,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8632,7 +8637,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8659,10 +8664,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118329053</v>
+        <v>118329098</v>
       </c>
       <c r="B73" t="n">
-        <v>79594</v>
+        <v>79566</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8671,25 +8676,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8699,10 +8704,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539176</v>
+        <v>539698</v>
       </c>
       <c r="R73" t="n">
-        <v>7199101</v>
+        <v>7198870</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8734,7 +8739,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8744,7 +8749,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8771,10 +8776,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118329139</v>
+        <v>118329057</v>
       </c>
       <c r="B74" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8783,25 +8788,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8811,10 +8816,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539448</v>
+        <v>539165</v>
       </c>
       <c r="R74" t="n">
-        <v>7199233</v>
+        <v>7198816</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8846,7 +8851,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8856,7 +8861,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8883,10 +8888,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118329081</v>
+        <v>118329073</v>
       </c>
       <c r="B75" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8899,39 +8904,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539471</v>
+        <v>539301</v>
       </c>
       <c r="R75" t="n">
-        <v>7198904</v>
+        <v>7198925</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9000,7 +9000,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118329060</v>
+        <v>118329082</v>
       </c>
       <c r="B76" t="n">
         <v>78484</v>
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539179</v>
+        <v>539469</v>
       </c>
       <c r="R76" t="n">
-        <v>7198796</v>
+        <v>7198907</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9112,10 +9112,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118329057</v>
+        <v>118329090</v>
       </c>
       <c r="B77" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9124,25 +9124,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539165</v>
+        <v>539689</v>
       </c>
       <c r="R77" t="n">
-        <v>7198816</v>
+        <v>7198811</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9224,10 +9224,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118329109</v>
+        <v>118329087</v>
       </c>
       <c r="B78" t="n">
-        <v>90500</v>
+        <v>79594</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9236,25 +9236,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539520</v>
+        <v>539639</v>
       </c>
       <c r="R78" t="n">
-        <v>7199044</v>
+        <v>7198854</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9336,7 +9336,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118329118</v>
+        <v>118329070</v>
       </c>
       <c r="B79" t="n">
         <v>90896</v>
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539499</v>
+        <v>539292</v>
       </c>
       <c r="R79" t="n">
-        <v>7199150</v>
+        <v>7198929</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9443,10 +9443,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118329079</v>
+        <v>118329138</v>
       </c>
       <c r="B80" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9455,25 +9455,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539381</v>
+        <v>539448</v>
       </c>
       <c r="R80" t="n">
-        <v>7198861</v>
+        <v>7199233</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9555,10 +9555,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118329133</v>
+        <v>118329136</v>
       </c>
       <c r="B81" t="n">
-        <v>97867</v>
+        <v>77421</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9567,25 +9567,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539424</v>
+        <v>539445</v>
       </c>
       <c r="R81" t="n">
-        <v>7199232</v>
+        <v>7199236</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -7315,10 +7315,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118329084</v>
+        <v>118329123</v>
       </c>
       <c r="B61" t="n">
-        <v>79601</v>
+        <v>96801</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7331,21 +7331,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7355,10 +7355,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539643</v>
+        <v>539449</v>
       </c>
       <c r="R61" t="n">
-        <v>7198846</v>
+        <v>7199143</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7427,10 +7427,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329115</v>
+        <v>118329084</v>
       </c>
       <c r="B62" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7443,21 +7443,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539543</v>
+        <v>539643</v>
       </c>
       <c r="R62" t="n">
-        <v>7199127</v>
+        <v>7198846</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329123</v>
+        <v>118329115</v>
       </c>
       <c r="B63" t="n">
-        <v>96801</v>
+        <v>79594</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7555,21 +7555,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539449</v>
+        <v>539543</v>
       </c>
       <c r="R63" t="n">
-        <v>7199143</v>
+        <v>7199127</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329110</v>
+        <v>118329053</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539520</v>
+        <v>539176</v>
       </c>
       <c r="R3" t="n">
-        <v>7199050</v>
+        <v>7199101</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329109</v>
+        <v>118329087</v>
       </c>
       <c r="B4" t="n">
-        <v>90500</v>
+        <v>79594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539520</v>
+        <v>539639</v>
       </c>
       <c r="R4" t="n">
-        <v>7199044</v>
+        <v>7198854</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329054</v>
+        <v>118329106</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,34 +1028,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539175</v>
+        <v>539537</v>
       </c>
       <c r="R5" t="n">
-        <v>7199103</v>
+        <v>7199040</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118329118</v>
+        <v>118329068</v>
       </c>
       <c r="B6" t="n">
-        <v>90896</v>
+        <v>90504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,16 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539499</v>
+        <v>539196</v>
       </c>
       <c r="R6" t="n">
-        <v>7199150</v>
+        <v>7198782</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1194,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329114</v>
+        <v>118329061</v>
       </c>
       <c r="B7" t="n">
-        <v>79566</v>
+        <v>82263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1257,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539540</v>
+        <v>539169</v>
       </c>
       <c r="R7" t="n">
-        <v>7199126</v>
+        <v>7198790</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1306,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1326,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329137</v>
+        <v>118329097</v>
       </c>
       <c r="B8" t="n">
-        <v>74596</v>
+        <v>97867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,25 +1365,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539448</v>
+        <v>539700</v>
       </c>
       <c r="R8" t="n">
-        <v>7199233</v>
+        <v>7198865</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329100</v>
+        <v>118329126</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1477,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539698</v>
+        <v>539448</v>
       </c>
       <c r="R9" t="n">
-        <v>7198866</v>
+        <v>7199142</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1530,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329056</v>
+        <v>118329139</v>
       </c>
       <c r="B10" t="n">
         <v>78484</v>
@@ -1607,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539183</v>
+        <v>539448</v>
       </c>
       <c r="R10" t="n">
-        <v>7198843</v>
+        <v>7199233</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1642,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,7 +1689,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329104</v>
+        <v>118329062</v>
       </c>
       <c r="B11" t="n">
         <v>78484</v>
@@ -1719,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539613</v>
+        <v>539168</v>
       </c>
       <c r="R11" t="n">
-        <v>7198921</v>
+        <v>7198788</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1754,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1764,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329053</v>
+        <v>118329099</v>
       </c>
       <c r="B12" t="n">
-        <v>79594</v>
+        <v>104925</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1831,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539176</v>
+        <v>539699</v>
       </c>
       <c r="R12" t="n">
-        <v>7199101</v>
+        <v>7198868</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1866,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329106</v>
+        <v>118329077</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>86820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,39 +1929,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539537</v>
+        <v>539355</v>
       </c>
       <c r="R13" t="n">
-        <v>7199040</v>
+        <v>7198883</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1983,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1993,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2025,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118329069</v>
+        <v>118329102</v>
       </c>
       <c r="B14" t="n">
         <v>78484</v>
@@ -2060,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539197</v>
+        <v>539699</v>
       </c>
       <c r="R14" t="n">
-        <v>7198784</v>
+        <v>7198863</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2095,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2137,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118329126</v>
+        <v>118329079</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2172,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539448</v>
+        <v>539381</v>
       </c>
       <c r="R15" t="n">
-        <v>7199142</v>
+        <v>7198861</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2207,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118329079</v>
+        <v>118329095</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,34 +2265,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539381</v>
+        <v>539705</v>
       </c>
       <c r="R16" t="n">
-        <v>7198861</v>
+        <v>7198856</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2319,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329074</v>
+        <v>118329114</v>
       </c>
       <c r="B17" t="n">
-        <v>90522</v>
+        <v>79566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,21 +2382,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539323</v>
+        <v>539540</v>
       </c>
       <c r="R17" t="n">
-        <v>7198881</v>
+        <v>7199126</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2431,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2441,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118329094</v>
+        <v>118329116</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2508,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539687</v>
+        <v>539546</v>
       </c>
       <c r="R18" t="n">
-        <v>7198809</v>
+        <v>7199128</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2543,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2553,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329103</v>
+        <v>118329124</v>
       </c>
       <c r="B19" t="n">
-        <v>56502</v>
+        <v>90858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,48 +2602,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>1506</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539613</v>
+        <v>539448</v>
       </c>
       <c r="R19" t="n">
-        <v>7198921</v>
+        <v>7199143</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329097</v>
+        <v>118329055</v>
       </c>
       <c r="B20" t="n">
-        <v>97867</v>
+        <v>90500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,25 +2714,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539700</v>
+        <v>539176</v>
       </c>
       <c r="R20" t="n">
-        <v>7198865</v>
+        <v>7198838</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329062</v>
+        <v>118329107</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539168</v>
+        <v>539536</v>
       </c>
       <c r="R21" t="n">
-        <v>7198788</v>
+        <v>7199040</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329076</v>
+        <v>118329127</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539323</v>
+        <v>539435</v>
       </c>
       <c r="R22" t="n">
-        <v>7198881</v>
+        <v>7199161</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329072</v>
+        <v>118329050</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
+        <v>94250</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,43 +3050,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539301</v>
+        <v>539191</v>
       </c>
       <c r="R23" t="n">
-        <v>7198925</v>
+        <v>7199130</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3118,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3128,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329052</v>
+        <v>118329120</v>
       </c>
       <c r="B24" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3167,25 +3162,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3195,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539175</v>
+        <v>539497</v>
       </c>
       <c r="R24" t="n">
-        <v>7199100</v>
+        <v>7199152</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3240,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329127</v>
+        <v>118329118</v>
       </c>
       <c r="B25" t="n">
-        <v>90504</v>
+        <v>90896</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,21 +3278,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3307,10 +3297,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539435</v>
+        <v>539499</v>
       </c>
       <c r="R25" t="n">
-        <v>7199161</v>
+        <v>7199150</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3342,7 +3332,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3352,7 +3342,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,7 +3369,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118329078</v>
+        <v>118329056</v>
       </c>
       <c r="B26" t="n">
         <v>78484</v>
@@ -3419,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539351</v>
+        <v>539183</v>
       </c>
       <c r="R26" t="n">
-        <v>7198894</v>
+        <v>7198843</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3454,7 +3444,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3464,7 +3454,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3491,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329124</v>
+        <v>118329082</v>
       </c>
       <c r="B27" t="n">
-        <v>90858</v>
+        <v>78484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,25 +3493,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3531,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539448</v>
+        <v>539469</v>
       </c>
       <c r="R27" t="n">
-        <v>7199143</v>
+        <v>7198907</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3566,7 +3556,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3576,7 +3566,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3603,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329060</v>
+        <v>118329074</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3619,21 +3609,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3643,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539179</v>
+        <v>539323</v>
       </c>
       <c r="R28" t="n">
-        <v>7198796</v>
+        <v>7198881</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3678,7 +3668,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3688,7 +3678,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3715,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329071</v>
+        <v>118329052</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,25 +3717,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3755,10 +3745,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539291</v>
+        <v>539175</v>
       </c>
       <c r="R29" t="n">
-        <v>7198926</v>
+        <v>7199100</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3790,7 +3780,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,7 +3790,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3827,10 +3817,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329050</v>
+        <v>118329072</v>
       </c>
       <c r="B30" t="n">
-        <v>94250</v>
+        <v>57306</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,38 +3829,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539191</v>
+        <v>539301</v>
       </c>
       <c r="R30" t="n">
-        <v>7199130</v>
+        <v>7198925</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3902,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3912,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3939,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329067</v>
+        <v>118329122</v>
       </c>
       <c r="B31" t="n">
         <v>78484</v>
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539188</v>
+        <v>539468</v>
       </c>
       <c r="R31" t="n">
-        <v>7198737</v>
+        <v>7199130</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4024,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329081</v>
+        <v>118329059</v>
       </c>
       <c r="B32" t="n">
-        <v>57306</v>
+        <v>90522</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,39 +4062,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539471</v>
+        <v>539179</v>
       </c>
       <c r="R32" t="n">
-        <v>7198904</v>
+        <v>7198796</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4131,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4141,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4168,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329055</v>
+        <v>118329060</v>
       </c>
       <c r="B33" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4184,21 +4174,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4208,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539176</v>
+        <v>539179</v>
       </c>
       <c r="R33" t="n">
-        <v>7198838</v>
+        <v>7198796</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4243,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4280,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329092</v>
+        <v>118329073</v>
       </c>
       <c r="B34" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,25 +4282,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +4310,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539689</v>
+        <v>539301</v>
       </c>
       <c r="R34" t="n">
-        <v>7198809</v>
+        <v>7198925</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4355,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4365,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329112</v>
+        <v>118329081</v>
       </c>
       <c r="B35" t="n">
-        <v>91196</v>
+        <v>57306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,38 +4394,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539541</v>
+        <v>539471</v>
       </c>
       <c r="R35" t="n">
-        <v>7199130</v>
+        <v>7198904</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4467,7 +4462,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4477,7 +4472,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4499,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118329107</v>
+        <v>118329133</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,25 +4511,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4539,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539536</v>
+        <v>539424</v>
       </c>
       <c r="R36" t="n">
-        <v>7199040</v>
+        <v>7199232</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4579,7 +4574,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4589,7 +4584,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4616,10 +4611,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329134</v>
+        <v>118329078</v>
       </c>
       <c r="B37" t="n">
-        <v>97766</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4628,23 +4623,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4652,10 +4651,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539421</v>
+        <v>539351</v>
       </c>
       <c r="R37" t="n">
-        <v>7199232</v>
+        <v>7198894</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4687,7 +4686,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4697,7 +4696,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4706,7 +4705,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4725,7 +4723,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329116</v>
+        <v>118329105</v>
       </c>
       <c r="B38" t="n">
         <v>78484</v>
@@ -4765,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539546</v>
+        <v>539569</v>
       </c>
       <c r="R38" t="n">
-        <v>7199128</v>
+        <v>7199018</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4800,7 +4798,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4808,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329064</v>
+        <v>118329063</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>96807</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4849,25 +4847,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4877,7 +4875,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539166</v>
+        <v>539165</v>
       </c>
       <c r="R39" t="n">
         <v>7198776</v>
@@ -4949,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329080</v>
+        <v>118329134</v>
       </c>
       <c r="B40" t="n">
-        <v>90451</v>
+        <v>97766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4961,27 +4959,23 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>112</v>
+        <v>223597</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4989,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539383</v>
+        <v>539421</v>
       </c>
       <c r="R40" t="n">
-        <v>7198860</v>
+        <v>7199232</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5024,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,6 +5037,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5061,10 +5056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329063</v>
+        <v>118329110</v>
       </c>
       <c r="B41" t="n">
-        <v>96807</v>
+        <v>78484</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5073,25 +5068,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5101,10 +5096,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539165</v>
+        <v>539520</v>
       </c>
       <c r="R41" t="n">
-        <v>7198776</v>
+        <v>7199050</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5136,7 +5131,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5146,7 +5141,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5168,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118329121</v>
+        <v>118329112</v>
       </c>
       <c r="B42" t="n">
-        <v>90522</v>
+        <v>91196</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,25 +5180,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5213,10 +5208,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539470</v>
+        <v>539541</v>
       </c>
       <c r="R42" t="n">
-        <v>7199132</v>
+        <v>7199130</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5258,7 +5253,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5285,7 +5280,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329139</v>
+        <v>118329064</v>
       </c>
       <c r="B43" t="n">
         <v>78484</v>
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>539448</v>
+        <v>539166</v>
       </c>
       <c r="R43" t="n">
-        <v>7199233</v>
+        <v>7198776</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5360,7 +5355,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5370,7 +5365,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,7 +5392,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329128</v>
+        <v>118329131</v>
       </c>
       <c r="B44" t="n">
         <v>78484</v>
@@ -5437,10 +5432,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539438</v>
+        <v>539434</v>
       </c>
       <c r="R44" t="n">
-        <v>7199164</v>
+        <v>7199188</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5472,7 +5467,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5482,7 +5477,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5509,10 +5504,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329093</v>
+        <v>118329091</v>
       </c>
       <c r="B45" t="n">
-        <v>79594</v>
+        <v>79566</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,25 +5516,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5549,7 +5544,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539687</v>
+        <v>539689</v>
       </c>
       <c r="R45" t="n">
         <v>7198809</v>
@@ -5621,10 +5616,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329113</v>
+        <v>118329092</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5633,25 +5628,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5661,10 +5656,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539540</v>
+        <v>539689</v>
       </c>
       <c r="R46" t="n">
-        <v>7199128</v>
+        <v>7198809</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5696,7 +5691,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5706,7 +5701,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5733,10 +5728,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329131</v>
+        <v>118329098</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>79566</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5749,21 +5744,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5773,10 +5768,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539434</v>
+        <v>539698</v>
       </c>
       <c r="R47" t="n">
-        <v>7199188</v>
+        <v>7198870</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5808,7 +5803,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5818,7 +5813,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5845,10 +5840,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329133</v>
+        <v>118329138</v>
       </c>
       <c r="B48" t="n">
-        <v>97867</v>
+        <v>96801</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5861,21 +5856,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5885,10 +5880,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539424</v>
+        <v>539448</v>
       </c>
       <c r="R48" t="n">
-        <v>7199232</v>
+        <v>7199233</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5920,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5930,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5957,10 +5952,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118329099</v>
+        <v>118329136</v>
       </c>
       <c r="B49" t="n">
-        <v>104925</v>
+        <v>77421</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5969,25 +5964,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5997,10 +5992,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539699</v>
+        <v>539445</v>
       </c>
       <c r="R49" t="n">
-        <v>7198868</v>
+        <v>7199236</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6032,7 +6027,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6042,7 +6037,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6069,10 +6064,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118329059</v>
+        <v>118329117</v>
       </c>
       <c r="B50" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,21 +6080,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539179</v>
+        <v>539502</v>
       </c>
       <c r="R50" t="n">
-        <v>7198796</v>
+        <v>7199148</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6144,7 +6139,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6154,7 +6149,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6181,7 +6176,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118329143</v>
+        <v>118329104</v>
       </c>
       <c r="B51" t="n">
         <v>78484</v>
@@ -6221,10 +6216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539470</v>
+        <v>539613</v>
       </c>
       <c r="R51" t="n">
-        <v>7199251</v>
+        <v>7198921</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6256,7 +6251,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6266,7 +6261,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6293,10 +6288,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118329111</v>
+        <v>118329100</v>
       </c>
       <c r="B52" t="n">
-        <v>82263</v>
+        <v>79594</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6305,25 +6300,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6333,10 +6328,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539540</v>
+        <v>539698</v>
       </c>
       <c r="R52" t="n">
-        <v>7199131</v>
+        <v>7198866</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6368,7 +6363,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6378,7 +6373,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6405,10 +6400,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118329122</v>
+        <v>118329070</v>
       </c>
       <c r="B53" t="n">
-        <v>78484</v>
+        <v>90896</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6421,21 +6416,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6445,10 +6435,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539468</v>
+        <v>539292</v>
       </c>
       <c r="R53" t="n">
-        <v>7199130</v>
+        <v>7198929</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6480,7 +6470,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6490,7 +6480,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6517,10 +6507,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118329085</v>
+        <v>118329109</v>
       </c>
       <c r="B54" t="n">
-        <v>79600</v>
+        <v>90500</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6529,25 +6519,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6557,10 +6547,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539640</v>
+        <v>539520</v>
       </c>
       <c r="R54" t="n">
-        <v>7198849</v>
+        <v>7199044</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6592,7 +6582,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6602,7 +6592,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6629,7 +6619,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118329120</v>
+        <v>118329058</v>
       </c>
       <c r="B55" t="n">
         <v>78484</v>
@@ -6669,10 +6659,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539497</v>
+        <v>539167</v>
       </c>
       <c r="R55" t="n">
-        <v>7199152</v>
+        <v>7198820</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6704,7 +6694,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6714,7 +6704,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6741,7 +6731,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118329102</v>
+        <v>118329069</v>
       </c>
       <c r="B56" t="n">
         <v>78484</v>
@@ -6781,10 +6771,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539699</v>
+        <v>539197</v>
       </c>
       <c r="R56" t="n">
-        <v>7198863</v>
+        <v>7198784</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6816,7 +6806,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6826,7 +6816,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6853,10 +6843,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118329083</v>
+        <v>118329057</v>
       </c>
       <c r="B57" t="n">
-        <v>57290</v>
+        <v>90469</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6865,52 +6855,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539604</v>
+        <v>539165</v>
       </c>
       <c r="R57" t="n">
-        <v>7198880</v>
+        <v>7198816</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6942,7 +6918,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6952,7 +6928,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6979,10 +6955,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118329125</v>
+        <v>118329085</v>
       </c>
       <c r="B58" t="n">
-        <v>90788</v>
+        <v>79600</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6991,25 +6967,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7019,10 +6995,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539448</v>
+        <v>539640</v>
       </c>
       <c r="R58" t="n">
-        <v>7199144</v>
+        <v>7198849</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7054,7 +7030,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7064,7 +7040,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7091,10 +7067,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118329077</v>
+        <v>118329084</v>
       </c>
       <c r="B59" t="n">
-        <v>86820</v>
+        <v>79601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7103,25 +7079,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7131,10 +7107,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539355</v>
+        <v>539643</v>
       </c>
       <c r="R59" t="n">
-        <v>7198883</v>
+        <v>7198846</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7166,7 +7142,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7176,7 +7152,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7203,10 +7179,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118329061</v>
+        <v>118329125</v>
       </c>
       <c r="B60" t="n">
-        <v>82263</v>
+        <v>90788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7219,21 +7195,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7243,10 +7219,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539169</v>
+        <v>539448</v>
       </c>
       <c r="R60" t="n">
-        <v>7198790</v>
+        <v>7199144</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7278,7 +7254,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7288,7 +7264,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7315,10 +7291,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118329123</v>
+        <v>118329065</v>
       </c>
       <c r="B61" t="n">
-        <v>96801</v>
+        <v>90522</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7327,25 +7303,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7355,10 +7331,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539449</v>
+        <v>539189</v>
       </c>
       <c r="R61" t="n">
-        <v>7199143</v>
+        <v>7198737</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7390,7 +7366,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7400,7 +7376,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7427,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329084</v>
+        <v>118329071</v>
       </c>
       <c r="B62" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7439,25 +7415,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7467,10 +7443,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539643</v>
+        <v>539291</v>
       </c>
       <c r="R62" t="n">
-        <v>7198846</v>
+        <v>7198926</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7502,7 +7478,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7512,7 +7488,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7539,10 +7515,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329115</v>
+        <v>118329111</v>
       </c>
       <c r="B63" t="n">
-        <v>79594</v>
+        <v>82263</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7551,25 +7527,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7579,10 +7555,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539543</v>
+        <v>539540</v>
       </c>
       <c r="R63" t="n">
-        <v>7199127</v>
+        <v>7199131</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7614,7 +7590,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7624,7 +7600,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7651,10 +7627,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118329058</v>
+        <v>118329137</v>
       </c>
       <c r="B64" t="n">
-        <v>78484</v>
+        <v>74596</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7667,21 +7643,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7691,10 +7667,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539167</v>
+        <v>539448</v>
       </c>
       <c r="R64" t="n">
-        <v>7198820</v>
+        <v>7199233</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7726,7 +7702,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7736,7 +7712,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7763,10 +7739,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118329065</v>
+        <v>118329113</v>
       </c>
       <c r="B65" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7779,21 +7755,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7803,10 +7779,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539189</v>
+        <v>539540</v>
       </c>
       <c r="R65" t="n">
-        <v>7198737</v>
+        <v>7199128</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7838,7 +7814,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7848,7 +7824,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7875,10 +7851,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118329091</v>
+        <v>118329067</v>
       </c>
       <c r="B66" t="n">
-        <v>79566</v>
+        <v>78484</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7891,21 +7867,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7915,10 +7891,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539689</v>
+        <v>539188</v>
       </c>
       <c r="R66" t="n">
-        <v>7198809</v>
+        <v>7198737</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7950,7 +7926,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7960,7 +7936,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7987,7 +7963,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118329117</v>
+        <v>118329051</v>
       </c>
       <c r="B67" t="n">
         <v>78484</v>
@@ -8027,10 +8003,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539502</v>
+        <v>539190</v>
       </c>
       <c r="R67" t="n">
-        <v>7199148</v>
+        <v>7199129</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8062,7 +8038,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8072,7 +8048,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8099,10 +8075,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118329119</v>
+        <v>118329080</v>
       </c>
       <c r="B68" t="n">
-        <v>82263</v>
+        <v>90451</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8115,21 +8091,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8139,10 +8115,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539499</v>
+        <v>539383</v>
       </c>
       <c r="R68" t="n">
-        <v>7199152</v>
+        <v>7198860</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8174,7 +8150,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8184,7 +8160,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8211,7 +8187,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118329105</v>
+        <v>118329128</v>
       </c>
       <c r="B69" t="n">
         <v>78484</v>
@@ -8251,10 +8227,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539569</v>
+        <v>539438</v>
       </c>
       <c r="R69" t="n">
-        <v>7199018</v>
+        <v>7199164</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8286,7 +8262,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8296,7 +8272,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8323,10 +8299,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118329095</v>
+        <v>118329143</v>
       </c>
       <c r="B70" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8339,39 +8315,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539705</v>
+        <v>539470</v>
       </c>
       <c r="R70" t="n">
-        <v>7198856</v>
+        <v>7199251</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8403,7 +8374,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8413,7 +8384,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8440,7 +8411,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118329051</v>
+        <v>118329094</v>
       </c>
       <c r="B71" t="n">
         <v>78484</v>
@@ -8480,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539190</v>
+        <v>539687</v>
       </c>
       <c r="R71" t="n">
-        <v>7199129</v>
+        <v>7198809</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8515,7 +8486,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8525,7 +8496,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,10 +8523,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118329068</v>
+        <v>118329090</v>
       </c>
       <c r="B72" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8568,21 +8539,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8592,10 +8563,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539196</v>
+        <v>539689</v>
       </c>
       <c r="R72" t="n">
-        <v>7198782</v>
+        <v>7198811</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8627,7 +8598,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8637,7 +8608,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8664,10 +8635,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118329098</v>
+        <v>118329093</v>
       </c>
       <c r="B73" t="n">
-        <v>79566</v>
+        <v>79594</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8676,25 +8647,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8704,10 +8675,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539698</v>
+        <v>539687</v>
       </c>
       <c r="R73" t="n">
-        <v>7198870</v>
+        <v>7198809</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8739,7 +8710,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8749,7 +8720,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8776,10 +8747,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118329057</v>
+        <v>118329115</v>
       </c>
       <c r="B74" t="n">
-        <v>90469</v>
+        <v>79594</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8792,21 +8763,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8816,10 +8787,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539165</v>
+        <v>539543</v>
       </c>
       <c r="R74" t="n">
-        <v>7198816</v>
+        <v>7199127</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8851,7 +8822,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8861,7 +8832,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8888,10 +8859,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118329073</v>
+        <v>118329083</v>
       </c>
       <c r="B75" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8904,34 +8875,48 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539301</v>
+        <v>539604</v>
       </c>
       <c r="R75" t="n">
-        <v>7198925</v>
+        <v>7198880</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8963,7 +8948,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8973,7 +8958,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9000,10 +8985,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118329082</v>
+        <v>118329123</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9012,25 +8997,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9040,10 +9025,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539469</v>
+        <v>539449</v>
       </c>
       <c r="R76" t="n">
-        <v>7198907</v>
+        <v>7199143</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9075,7 +9060,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9085,7 +9070,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9112,10 +9097,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118329090</v>
+        <v>118329054</v>
       </c>
       <c r="B77" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9128,21 +9113,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9152,10 +9137,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539689</v>
+        <v>539175</v>
       </c>
       <c r="R77" t="n">
-        <v>7198811</v>
+        <v>7199103</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9187,7 +9172,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9197,7 +9182,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9224,10 +9209,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118329087</v>
+        <v>118329076</v>
       </c>
       <c r="B78" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9236,25 +9221,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9264,10 +9249,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539639</v>
+        <v>539323</v>
       </c>
       <c r="R78" t="n">
-        <v>7198854</v>
+        <v>7198881</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9299,7 +9284,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9309,7 +9294,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9336,10 +9321,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118329070</v>
+        <v>118329103</v>
       </c>
       <c r="B79" t="n">
-        <v>90896</v>
+        <v>56502</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9348,33 +9333,48 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6040186</v>
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539292</v>
+        <v>539613</v>
       </c>
       <c r="R79" t="n">
-        <v>7198929</v>
+        <v>7198921</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9443,10 +9443,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118329138</v>
+        <v>118329121</v>
       </c>
       <c r="B80" t="n">
-        <v>96801</v>
+        <v>90522</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9455,25 +9455,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539448</v>
+        <v>539470</v>
       </c>
       <c r="R80" t="n">
-        <v>7199233</v>
+        <v>7199132</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9555,10 +9555,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118329136</v>
+        <v>118329119</v>
       </c>
       <c r="B81" t="n">
-        <v>77421</v>
+        <v>82263</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9571,21 +9571,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539445</v>
+        <v>539499</v>
       </c>
       <c r="R81" t="n">
-        <v>7199236</v>
+        <v>7199152</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329053</v>
+        <v>118329103</v>
       </c>
       <c r="B3" t="n">
-        <v>79594</v>
+        <v>56502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,34 +804,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539176</v>
+        <v>539613</v>
       </c>
       <c r="R3" t="n">
-        <v>7199101</v>
+        <v>7198921</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329087</v>
+        <v>118329080</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
+        <v>90458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +922,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539639</v>
+        <v>539383</v>
       </c>
       <c r="R4" t="n">
-        <v>7198854</v>
+        <v>7198860</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329106</v>
+        <v>118329078</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,39 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539537</v>
+        <v>539351</v>
       </c>
       <c r="R5" t="n">
-        <v>7199040</v>
+        <v>7198894</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118329068</v>
+        <v>118329073</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539196</v>
+        <v>539301</v>
       </c>
       <c r="R6" t="n">
-        <v>7198782</v>
+        <v>7198925</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329061</v>
+        <v>118329115</v>
       </c>
       <c r="B7" t="n">
-        <v>82263</v>
+        <v>79601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539169</v>
+        <v>539543</v>
       </c>
       <c r="R7" t="n">
-        <v>7198790</v>
+        <v>7199127</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329097</v>
+        <v>118329118</v>
       </c>
       <c r="B8" t="n">
-        <v>97867</v>
+        <v>90903</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,25 +1370,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539700</v>
+        <v>539499</v>
       </c>
       <c r="R8" t="n">
-        <v>7198865</v>
+        <v>7199150</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329126</v>
+        <v>118329069</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539448</v>
+        <v>539197</v>
       </c>
       <c r="R9" t="n">
-        <v>7199142</v>
+        <v>7198784</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329139</v>
+        <v>118329107</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539448</v>
+        <v>539536</v>
       </c>
       <c r="R10" t="n">
-        <v>7199233</v>
+        <v>7199040</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329062</v>
+        <v>118329060</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539168</v>
+        <v>539179</v>
       </c>
       <c r="R11" t="n">
-        <v>7198788</v>
+        <v>7198796</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329099</v>
+        <v>118329121</v>
       </c>
       <c r="B12" t="n">
-        <v>104925</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539699</v>
+        <v>539470</v>
       </c>
       <c r="R12" t="n">
-        <v>7198868</v>
+        <v>7199132</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329077</v>
+        <v>118329084</v>
       </c>
       <c r="B13" t="n">
-        <v>86820</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539355</v>
+        <v>539643</v>
       </c>
       <c r="R13" t="n">
-        <v>7198883</v>
+        <v>7198846</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118329102</v>
+        <v>118329092</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,25 +2037,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539699</v>
+        <v>539689</v>
       </c>
       <c r="R14" t="n">
-        <v>7198863</v>
+        <v>7198809</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118329079</v>
+        <v>118329098</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>79573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539381</v>
+        <v>539698</v>
       </c>
       <c r="R15" t="n">
-        <v>7198861</v>
+        <v>7198870</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118329095</v>
+        <v>118329124</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>90865</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,43 +2261,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539705</v>
+        <v>539448</v>
       </c>
       <c r="R16" t="n">
-        <v>7198856</v>
+        <v>7199143</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329114</v>
+        <v>118329077</v>
       </c>
       <c r="B17" t="n">
-        <v>79566</v>
+        <v>86827</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539540</v>
+        <v>539355</v>
       </c>
       <c r="R17" t="n">
-        <v>7199126</v>
+        <v>7198883</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2441,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2446,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118329116</v>
+        <v>118329138</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>96808</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539546</v>
+        <v>539448</v>
       </c>
       <c r="R18" t="n">
-        <v>7199128</v>
+        <v>7199233</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2553,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2558,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329124</v>
+        <v>118329059</v>
       </c>
       <c r="B19" t="n">
-        <v>90858</v>
+        <v>90529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,25 +2597,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2630,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539448</v>
+        <v>539179</v>
       </c>
       <c r="R19" t="n">
-        <v>7199143</v>
+        <v>7198796</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2665,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329055</v>
+        <v>118329120</v>
       </c>
       <c r="B20" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539176</v>
+        <v>539497</v>
       </c>
       <c r="R20" t="n">
-        <v>7198838</v>
+        <v>7199152</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2782,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329107</v>
+        <v>118329083</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,34 +2825,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539536</v>
+        <v>539604</v>
       </c>
       <c r="R21" t="n">
-        <v>7199040</v>
+        <v>7198880</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329127</v>
+        <v>118329055</v>
       </c>
       <c r="B22" t="n">
-        <v>90504</v>
+        <v>90507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539435</v>
+        <v>539176</v>
       </c>
       <c r="R22" t="n">
-        <v>7199161</v>
+        <v>7198838</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329050</v>
+        <v>118329094</v>
       </c>
       <c r="B23" t="n">
-        <v>94250</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,25 +3059,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +3087,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539191</v>
+        <v>539687</v>
       </c>
       <c r="R23" t="n">
-        <v>7199130</v>
+        <v>7198809</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3113,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329120</v>
+        <v>118329093</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,25 +3171,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539497</v>
+        <v>539687</v>
       </c>
       <c r="R24" t="n">
-        <v>7199152</v>
+        <v>7198809</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3225,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329118</v>
+        <v>118329116</v>
       </c>
       <c r="B25" t="n">
-        <v>90896</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,16 +3287,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539499</v>
+        <v>539546</v>
       </c>
       <c r="R25" t="n">
-        <v>7199150</v>
+        <v>7199128</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3332,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3342,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3369,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118329056</v>
+        <v>118329122</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3409,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539183</v>
+        <v>539468</v>
       </c>
       <c r="R26" t="n">
-        <v>7198843</v>
+        <v>7199130</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3444,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3454,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329082</v>
+        <v>118329087</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,25 +3507,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3521,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539469</v>
+        <v>539639</v>
       </c>
       <c r="R27" t="n">
-        <v>7198907</v>
+        <v>7198854</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3556,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3566,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3593,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329074</v>
+        <v>118329097</v>
       </c>
       <c r="B28" t="n">
-        <v>90522</v>
+        <v>97874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,25 +3619,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3633,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539323</v>
+        <v>539700</v>
       </c>
       <c r="R28" t="n">
-        <v>7198881</v>
+        <v>7198865</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3678,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3705,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329052</v>
+        <v>118329070</v>
       </c>
       <c r="B29" t="n">
-        <v>79601</v>
+        <v>90903</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3717,25 +3731,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3745,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539175</v>
+        <v>539292</v>
       </c>
       <c r="R29" t="n">
-        <v>7199100</v>
+        <v>7198929</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3780,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3790,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3817,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329072</v>
+        <v>118329071</v>
       </c>
       <c r="B30" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,39 +3842,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539301</v>
+        <v>539291</v>
       </c>
       <c r="R30" t="n">
-        <v>7198925</v>
+        <v>7198926</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3897,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,10 +3938,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329122</v>
+        <v>118329090</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3950,21 +3954,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3974,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539468</v>
+        <v>539689</v>
       </c>
       <c r="R31" t="n">
-        <v>7199130</v>
+        <v>7198811</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4009,7 +4013,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4023,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329059</v>
+        <v>118329104</v>
       </c>
       <c r="B32" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,21 +4066,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4086,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539179</v>
+        <v>539613</v>
       </c>
       <c r="R32" t="n">
-        <v>7198796</v>
+        <v>7198921</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4121,7 +4125,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4135,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329060</v>
+        <v>118329126</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>539179</v>
+        <v>539448</v>
       </c>
       <c r="R33" t="n">
-        <v>7198796</v>
+        <v>7199142</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4233,7 +4237,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4247,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329073</v>
+        <v>118329128</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539301</v>
+        <v>539438</v>
       </c>
       <c r="R34" t="n">
-        <v>7198925</v>
+        <v>7199164</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4345,7 +4349,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4359,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4386,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329081</v>
+        <v>118329113</v>
       </c>
       <c r="B35" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4398,39 +4402,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539471</v>
+        <v>539540</v>
       </c>
       <c r="R35" t="n">
-        <v>7198904</v>
+        <v>7199128</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4462,7 +4461,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4472,7 +4471,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4499,10 +4498,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118329133</v>
+        <v>118329053</v>
       </c>
       <c r="B36" t="n">
-        <v>97867</v>
+        <v>79601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,21 +4514,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4539,10 +4538,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539424</v>
+        <v>539176</v>
       </c>
       <c r="R36" t="n">
-        <v>7199232</v>
+        <v>7199101</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4574,7 +4573,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4584,7 +4583,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4611,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329078</v>
+        <v>118329100</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4651,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539351</v>
+        <v>539698</v>
       </c>
       <c r="R37" t="n">
-        <v>7198894</v>
+        <v>7198866</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4686,7 +4685,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4696,7 +4695,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4723,10 +4722,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329105</v>
+        <v>118329109</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>90507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4739,21 +4738,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4763,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539569</v>
+        <v>539520</v>
       </c>
       <c r="R38" t="n">
-        <v>7199018</v>
+        <v>7199044</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4798,7 +4797,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4808,7 +4807,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329063</v>
+        <v>118329114</v>
       </c>
       <c r="B39" t="n">
-        <v>96807</v>
+        <v>79573</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,25 +4846,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4875,10 +4874,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539165</v>
+        <v>539540</v>
       </c>
       <c r="R39" t="n">
-        <v>7198776</v>
+        <v>7199126</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4910,7 +4909,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4920,7 +4919,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4947,10 +4946,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329134</v>
+        <v>118329062</v>
       </c>
       <c r="B40" t="n">
-        <v>97766</v>
+        <v>78491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,23 +4958,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4983,10 +4986,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539421</v>
+        <v>539168</v>
       </c>
       <c r="R40" t="n">
-        <v>7199232</v>
+        <v>7198788</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5018,7 +5021,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5031,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5037,7 +5040,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5056,10 +5058,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329110</v>
+        <v>118329082</v>
       </c>
       <c r="B41" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5096,10 +5098,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539520</v>
+        <v>539469</v>
       </c>
       <c r="R41" t="n">
-        <v>7199050</v>
+        <v>7198907</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,7 +5133,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5143,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,10 +5170,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118329112</v>
+        <v>118329117</v>
       </c>
       <c r="B42" t="n">
-        <v>91196</v>
+        <v>78491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5180,25 +5182,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5208,10 +5210,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>539541</v>
+        <v>539502</v>
       </c>
       <c r="R42" t="n">
-        <v>7199130</v>
+        <v>7199148</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5243,7 +5245,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5253,7 +5255,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,7 +5285,7 @@
         <v>118329064</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5392,10 +5394,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329131</v>
+        <v>118329134</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>97773</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5404,27 +5406,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5432,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>539434</v>
+        <v>539421</v>
       </c>
       <c r="R44" t="n">
-        <v>7199188</v>
+        <v>7199232</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5467,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5477,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,6 +5484,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5504,10 +5503,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329091</v>
+        <v>118329136</v>
       </c>
       <c r="B45" t="n">
-        <v>79566</v>
+        <v>77428</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5520,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5544,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>539689</v>
+        <v>539445</v>
       </c>
       <c r="R45" t="n">
-        <v>7198809</v>
+        <v>7199236</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5579,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5589,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329092</v>
+        <v>118329137</v>
       </c>
       <c r="B46" t="n">
-        <v>79601</v>
+        <v>74603</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5628,25 +5627,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5656,10 +5655,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>539689</v>
+        <v>539448</v>
       </c>
       <c r="R46" t="n">
-        <v>7198809</v>
+        <v>7199233</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5691,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5701,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5728,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329098</v>
+        <v>118329131</v>
       </c>
       <c r="B47" t="n">
-        <v>79566</v>
+        <v>78491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5744,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5768,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>539698</v>
+        <v>539434</v>
       </c>
       <c r="R47" t="n">
-        <v>7198870</v>
+        <v>7199188</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5803,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5813,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5840,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329138</v>
+        <v>118329112</v>
       </c>
       <c r="B48" t="n">
-        <v>96801</v>
+        <v>91203</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5856,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5880,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539448</v>
+        <v>539541</v>
       </c>
       <c r="R48" t="n">
-        <v>7199233</v>
+        <v>7199130</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5915,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5952,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118329136</v>
+        <v>118329068</v>
       </c>
       <c r="B49" t="n">
-        <v>77421</v>
+        <v>90511</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5968,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5992,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539445</v>
+        <v>539196</v>
       </c>
       <c r="R49" t="n">
-        <v>7199236</v>
+        <v>7198782</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6027,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6037,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6064,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118329117</v>
+        <v>118329119</v>
       </c>
       <c r="B50" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,21 +6079,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6104,10 +6103,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539502</v>
+        <v>539499</v>
       </c>
       <c r="R50" t="n">
-        <v>7199148</v>
+        <v>7199152</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6139,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6149,7 +6148,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6176,10 +6175,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118329104</v>
+        <v>118329072</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6192,34 +6191,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539613</v>
+        <v>539301</v>
       </c>
       <c r="R51" t="n">
-        <v>7198921</v>
+        <v>7198925</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6251,7 +6255,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6288,10 +6292,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118329100</v>
+        <v>118329063</v>
       </c>
       <c r="B52" t="n">
-        <v>79594</v>
+        <v>96814</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6304,21 +6308,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6328,10 +6332,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539698</v>
+        <v>539165</v>
       </c>
       <c r="R52" t="n">
-        <v>7198866</v>
+        <v>7198776</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6363,7 +6367,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6373,7 +6377,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6400,10 +6404,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118329070</v>
+        <v>118329127</v>
       </c>
       <c r="B53" t="n">
-        <v>90896</v>
+        <v>90511</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6416,16 +6420,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6435,10 +6444,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>539292</v>
+        <v>539435</v>
       </c>
       <c r="R53" t="n">
-        <v>7198929</v>
+        <v>7199161</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6470,7 +6479,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6480,7 +6489,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6507,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118329109</v>
+        <v>118329054</v>
       </c>
       <c r="B54" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6523,21 +6532,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6547,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539520</v>
+        <v>539175</v>
       </c>
       <c r="R54" t="n">
-        <v>7199044</v>
+        <v>7199103</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6582,7 +6591,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6592,7 +6601,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6619,10 +6628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118329058</v>
+        <v>118329105</v>
       </c>
       <c r="B55" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6659,10 +6668,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>539167</v>
+        <v>539569</v>
       </c>
       <c r="R55" t="n">
-        <v>7198820</v>
+        <v>7199018</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6694,7 +6703,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6704,7 +6713,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6731,10 +6740,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118329069</v>
+        <v>118329095</v>
       </c>
       <c r="B56" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6747,34 +6756,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539197</v>
+        <v>539705</v>
       </c>
       <c r="R56" t="n">
-        <v>7198784</v>
+        <v>7198856</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6806,7 +6820,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6816,7 +6830,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6843,10 +6857,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118329057</v>
+        <v>118329133</v>
       </c>
       <c r="B57" t="n">
-        <v>90469</v>
+        <v>97874</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6859,21 +6873,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6883,10 +6897,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539165</v>
+        <v>539424</v>
       </c>
       <c r="R57" t="n">
-        <v>7198816</v>
+        <v>7199232</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6918,7 +6932,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6928,7 +6942,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6955,10 +6969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118329085</v>
+        <v>118329051</v>
       </c>
       <c r="B58" t="n">
-        <v>79600</v>
+        <v>78491</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6967,20 +6981,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6995,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539640</v>
+        <v>539190</v>
       </c>
       <c r="R58" t="n">
-        <v>7198849</v>
+        <v>7199129</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7030,7 +7044,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7040,7 +7054,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7067,10 +7081,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118329084</v>
+        <v>118329065</v>
       </c>
       <c r="B59" t="n">
-        <v>79601</v>
+        <v>90529</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7079,25 +7093,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7107,10 +7121,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539643</v>
+        <v>539189</v>
       </c>
       <c r="R59" t="n">
-        <v>7198846</v>
+        <v>7198737</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7142,7 +7156,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7152,7 +7166,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7179,10 +7193,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118329125</v>
+        <v>118329085</v>
       </c>
       <c r="B60" t="n">
-        <v>90788</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7191,25 +7205,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7219,10 +7233,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539448</v>
+        <v>539640</v>
       </c>
       <c r="R60" t="n">
-        <v>7199144</v>
+        <v>7198849</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7254,7 +7268,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7264,7 +7278,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7291,10 +7305,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118329065</v>
+        <v>118329110</v>
       </c>
       <c r="B61" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7307,21 +7321,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7331,10 +7345,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539189</v>
+        <v>539520</v>
       </c>
       <c r="R61" t="n">
-        <v>7198737</v>
+        <v>7199050</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7366,7 +7380,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7376,7 +7390,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7403,10 +7417,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329071</v>
+        <v>118329139</v>
       </c>
       <c r="B62" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7443,10 +7457,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539291</v>
+        <v>539448</v>
       </c>
       <c r="R62" t="n">
-        <v>7198926</v>
+        <v>7199233</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7478,7 +7492,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7488,7 +7502,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7515,10 +7529,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329111</v>
+        <v>118329067</v>
       </c>
       <c r="B63" t="n">
-        <v>82263</v>
+        <v>78491</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7531,21 +7545,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7555,10 +7569,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539540</v>
+        <v>539188</v>
       </c>
       <c r="R63" t="n">
-        <v>7199131</v>
+        <v>7198737</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7590,7 +7604,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7600,7 +7614,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7627,10 +7641,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118329137</v>
+        <v>118329076</v>
       </c>
       <c r="B64" t="n">
-        <v>74596</v>
+        <v>78491</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7643,21 +7657,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7667,10 +7681,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539448</v>
+        <v>539323</v>
       </c>
       <c r="R64" t="n">
-        <v>7199233</v>
+        <v>7198881</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7702,7 +7716,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7712,7 +7726,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7739,10 +7753,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118329113</v>
+        <v>118329061</v>
       </c>
       <c r="B65" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7755,21 +7769,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7779,10 +7793,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>539540</v>
+        <v>539169</v>
       </c>
       <c r="R65" t="n">
-        <v>7199128</v>
+        <v>7198790</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7814,7 +7828,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7824,7 +7838,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7851,10 +7865,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118329067</v>
+        <v>118329091</v>
       </c>
       <c r="B66" t="n">
-        <v>78484</v>
+        <v>79573</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7867,21 +7881,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7891,10 +7905,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>539188</v>
+        <v>539689</v>
       </c>
       <c r="R66" t="n">
-        <v>7198737</v>
+        <v>7198809</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7926,7 +7940,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7936,7 +7950,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7963,10 +7977,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118329051</v>
+        <v>118329111</v>
       </c>
       <c r="B67" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7979,21 +7993,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8003,10 +8017,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>539190</v>
+        <v>539540</v>
       </c>
       <c r="R67" t="n">
-        <v>7199129</v>
+        <v>7199131</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8038,7 +8052,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8048,7 +8062,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8075,10 +8089,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118329080</v>
+        <v>118329106</v>
       </c>
       <c r="B68" t="n">
-        <v>90451</v>
+        <v>57290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8091,34 +8105,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539383</v>
+        <v>539537</v>
       </c>
       <c r="R68" t="n">
-        <v>7198860</v>
+        <v>7199040</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8150,7 +8169,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8160,7 +8179,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8187,10 +8206,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118329128</v>
+        <v>118329102</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8227,10 +8246,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539438</v>
+        <v>539699</v>
       </c>
       <c r="R69" t="n">
-        <v>7199164</v>
+        <v>7198863</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8262,7 +8281,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8272,7 +8291,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8299,10 +8318,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118329143</v>
+        <v>118329052</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8311,25 +8330,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8339,10 +8358,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539470</v>
+        <v>539175</v>
       </c>
       <c r="R70" t="n">
-        <v>7199251</v>
+        <v>7199100</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8374,7 +8393,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8384,7 +8403,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8411,10 +8430,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118329094</v>
+        <v>118329058</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8451,10 +8470,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539687</v>
+        <v>539167</v>
       </c>
       <c r="R71" t="n">
-        <v>7198809</v>
+        <v>7198820</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8486,7 +8505,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8496,7 +8515,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8523,10 +8542,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118329090</v>
+        <v>118329143</v>
       </c>
       <c r="B72" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8539,21 +8558,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8563,10 +8582,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539689</v>
+        <v>539470</v>
       </c>
       <c r="R72" t="n">
-        <v>7198811</v>
+        <v>7199251</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8598,7 +8617,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8608,7 +8627,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8635,10 +8654,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118329093</v>
+        <v>118329057</v>
       </c>
       <c r="B73" t="n">
-        <v>79594</v>
+        <v>90476</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8651,21 +8670,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8675,10 +8694,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539687</v>
+        <v>539165</v>
       </c>
       <c r="R73" t="n">
-        <v>7198809</v>
+        <v>7198816</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8710,7 +8729,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8720,7 +8739,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8747,10 +8766,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118329115</v>
+        <v>118329123</v>
       </c>
       <c r="B74" t="n">
-        <v>79594</v>
+        <v>96808</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8763,21 +8782,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8787,10 +8806,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539543</v>
+        <v>539449</v>
       </c>
       <c r="R74" t="n">
-        <v>7199127</v>
+        <v>7199143</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8822,7 +8841,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8832,7 +8851,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8859,10 +8878,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118329083</v>
+        <v>118329079</v>
       </c>
       <c r="B75" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8875,48 +8894,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539604</v>
+        <v>539381</v>
       </c>
       <c r="R75" t="n">
-        <v>7198880</v>
+        <v>7198861</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8948,7 +8953,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8958,7 +8963,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8985,10 +8990,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118329123</v>
+        <v>118329125</v>
       </c>
       <c r="B76" t="n">
-        <v>96801</v>
+        <v>90795</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8997,25 +9002,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9025,10 +9030,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539449</v>
+        <v>539448</v>
       </c>
       <c r="R76" t="n">
-        <v>7199143</v>
+        <v>7199144</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9060,7 +9065,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9070,7 +9075,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9097,10 +9102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118329054</v>
+        <v>118329056</v>
       </c>
       <c r="B77" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9137,10 +9142,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539175</v>
+        <v>539183</v>
       </c>
       <c r="R77" t="n">
-        <v>7199103</v>
+        <v>7198843</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9172,7 +9177,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9182,7 +9187,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9209,10 +9214,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118329076</v>
+        <v>118329074</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9225,21 +9230,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9321,10 +9326,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118329103</v>
+        <v>118329099</v>
       </c>
       <c r="B79" t="n">
-        <v>56502</v>
+        <v>104932</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9337,44 +9342,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539613</v>
+        <v>539699</v>
       </c>
       <c r="R79" t="n">
-        <v>7198921</v>
+        <v>7198868</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9406,7 +9401,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9416,7 +9411,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9443,10 +9438,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118329121</v>
+        <v>118329050</v>
       </c>
       <c r="B80" t="n">
-        <v>90522</v>
+        <v>94257</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9455,25 +9450,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9483,10 +9478,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539470</v>
+        <v>539191</v>
       </c>
       <c r="R80" t="n">
-        <v>7199132</v>
+        <v>7199130</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9518,7 +9513,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9528,7 +9523,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9555,10 +9550,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118329119</v>
+        <v>118329081</v>
       </c>
       <c r="B81" t="n">
-        <v>82263</v>
+        <v>57306</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9571,34 +9566,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539499</v>
+        <v>539471</v>
       </c>
       <c r="R81" t="n">
-        <v>7199152</v>
+        <v>7198904</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -2473,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118329138</v>
+        <v>118329059</v>
       </c>
       <c r="B18" t="n">
-        <v>96808</v>
+        <v>90529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,25 +2485,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539448</v>
+        <v>539179</v>
       </c>
       <c r="R18" t="n">
-        <v>7199233</v>
+        <v>7198796</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329059</v>
+        <v>118329120</v>
       </c>
       <c r="B19" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539179</v>
+        <v>539497</v>
       </c>
       <c r="R19" t="n">
-        <v>7198796</v>
+        <v>7199152</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329120</v>
+        <v>118329138</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>96808</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,25 +2709,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539497</v>
+        <v>539448</v>
       </c>
       <c r="R20" t="n">
-        <v>7199152</v>
+        <v>7199233</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329055</v>
+        <v>118329094</v>
       </c>
       <c r="B22" t="n">
-        <v>90507</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539176</v>
+        <v>539687</v>
       </c>
       <c r="R22" t="n">
-        <v>7198838</v>
+        <v>7198809</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329094</v>
+        <v>118329093</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>79601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,25 +3059,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329093</v>
+        <v>118329055</v>
       </c>
       <c r="B24" t="n">
-        <v>79601</v>
+        <v>90507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,25 +3171,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539687</v>
+        <v>539176</v>
       </c>
       <c r="R24" t="n">
-        <v>7198809</v>
+        <v>7198838</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118329133</v>
+        <v>118329051</v>
       </c>
       <c r="B57" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6869,25 +6869,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539424</v>
+        <v>539190</v>
       </c>
       <c r="R57" t="n">
-        <v>7199232</v>
+        <v>7199129</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,10 +6969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118329051</v>
+        <v>118329065</v>
       </c>
       <c r="B58" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6985,21 +6985,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539190</v>
+        <v>539189</v>
       </c>
       <c r="R58" t="n">
-        <v>7199129</v>
+        <v>7198737</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7081,10 +7081,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118329065</v>
+        <v>118329085</v>
       </c>
       <c r="B59" t="n">
-        <v>90529</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7093,25 +7093,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>539189</v>
+        <v>539640</v>
       </c>
       <c r="R59" t="n">
-        <v>7198737</v>
+        <v>7198849</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7193,10 +7193,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118329085</v>
+        <v>118329110</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>78491</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7205,20 +7205,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>539640</v>
+        <v>539520</v>
       </c>
       <c r="R60" t="n">
-        <v>7198849</v>
+        <v>7199050</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7305,7 +7305,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118329110</v>
+        <v>118329139</v>
       </c>
       <c r="B61" t="n">
         <v>78491</v>
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539520</v>
+        <v>539448</v>
       </c>
       <c r="R61" t="n">
-        <v>7199050</v>
+        <v>7199233</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7417,7 +7417,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118329139</v>
+        <v>118329067</v>
       </c>
       <c r="B62" t="n">
         <v>78491</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539448</v>
+        <v>539188</v>
       </c>
       <c r="R62" t="n">
-        <v>7199233</v>
+        <v>7198737</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7529,7 +7529,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118329067</v>
+        <v>118329076</v>
       </c>
       <c r="B63" t="n">
         <v>78491</v>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539188</v>
+        <v>539323</v>
       </c>
       <c r="R63" t="n">
-        <v>7198737</v>
+        <v>7198881</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7641,10 +7641,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118329076</v>
+        <v>118329133</v>
       </c>
       <c r="B64" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7653,25 +7653,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539323</v>
+        <v>539424</v>
       </c>
       <c r="R64" t="n">
-        <v>7198881</v>
+        <v>7199232</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8089,10 +8089,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118329106</v>
+        <v>118329102</v>
       </c>
       <c r="B68" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8105,39 +8105,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539537</v>
+        <v>539699</v>
       </c>
       <c r="R68" t="n">
-        <v>7199040</v>
+        <v>7198863</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8169,7 +8164,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8179,7 +8174,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8206,10 +8201,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118329102</v>
+        <v>118329106</v>
       </c>
       <c r="B69" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,34 +8217,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539699</v>
+        <v>539537</v>
       </c>
       <c r="R69" t="n">
-        <v>7198863</v>
+        <v>7199040</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 21943-2024 artfynd.xlsx
+++ b/artfynd/A 21943-2024 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>118329083</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
